--- a/england_premier-league-2024-2025.xlsx
+++ b/england_premier-league-2024-2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR251"/>
+  <dimension ref="A1:BR252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61958,6 +61958,354 @@
       </c>
       <c r="BR251" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>hxj39Vm2</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>19.02.2025</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ENGLAND</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>PREMIER LEAGUE - ROUND 29</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>["38'", "45+3'"]</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>["29'", "61'"]</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AT252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>84% (377/448)</t>
+        </is>
+      </c>
+      <c r="BD252" t="inlineStr">
+        <is>
+          <t>84% (341/404)</t>
+        </is>
+      </c>
+      <c r="BE252" t="inlineStr">
+        <is>
+          <t>69% (88/127)</t>
+        </is>
+      </c>
+      <c r="BF252" t="inlineStr">
+        <is>
+          <t>75% (92/122)</t>
+        </is>
+      </c>
+      <c r="BG252" t="inlineStr">
+        <is>
+          <t>21% (4/19)</t>
+        </is>
+      </c>
+      <c r="BH252" t="inlineStr">
+        <is>
+          <t>14% (3/21)</t>
+        </is>
+      </c>
+      <c r="BI252" t="inlineStr">
+        <is>
+          <t>55% (12/22)</t>
+        </is>
+      </c>
+      <c r="BJ252" t="inlineStr">
+        <is>
+          <t>73% (11/15)</t>
+        </is>
+      </c>
+      <c r="BK252" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BL252" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BM252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN252" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BO252" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP252" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BR252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
